--- a/gerber/mainboardv3.4-bom.xlsx
+++ b/gerber/mainboardv3.4-bom.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="120">
   <si>
     <t xml:space="preserve">Designator</t>
   </si>
@@ -28,7 +28,7 @@
     <t xml:space="preserve">Comment</t>
   </si>
   <si>
-    <t xml:space="preserve">Package</t>
+    <t xml:space="preserve">Footprint</t>
   </si>
   <si>
     <t xml:space="preserve">LCSC Part #</t>
@@ -58,7 +58,7 @@
     <t xml:space="preserve">C15850 </t>
   </si>
   <si>
-    <t xml:space="preserve">C11, C12, C12, C38, C41, C42 </t>
+    <t xml:space="preserve">C11, C12, C38, C41, C42 </t>
   </si>
   <si>
     <t xml:space="preserve">1nF</t>
@@ -91,7 +91,7 @@
     <t xml:space="preserve">SMD-ECAP-6.3X7.7</t>
   </si>
   <si>
-    <t xml:space="preserve">C134738</t>
+    <t xml:space="preserve">C72520</t>
   </si>
   <si>
     <t xml:space="preserve">C45</t>
@@ -163,7 +163,7 @@
     <t xml:space="preserve">TO263-5</t>
   </si>
   <si>
-    <t xml:space="preserve">C10002 </t>
+    <t xml:space="preserve">C194349</t>
   </si>
   <si>
     <t xml:space="preserve">IC2</t>
@@ -196,7 +196,7 @@
     <t xml:space="preserve">LQFP-64_10.0x10.0x0.5P</t>
   </si>
   <si>
-    <t xml:space="preserve">C8735 </t>
+    <t xml:space="preserve">C8735</t>
   </si>
   <si>
     <t xml:space="preserve">IC5</t>
@@ -232,7 +232,7 @@
     <t xml:space="preserve">SO14</t>
   </si>
   <si>
-    <t xml:space="preserve">C142961 </t>
+    <t xml:space="preserve">C5236698 </t>
   </si>
   <si>
     <t xml:space="preserve">IC8</t>
@@ -250,13 +250,13 @@
     <t xml:space="preserve">IC9</t>
   </si>
   <si>
-    <t xml:space="preserve">SN74LVC1G10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOT-23-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C258149</t>
+    <t xml:space="preserve">SN74AUP1G00DCKR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC-70-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C206053</t>
   </si>
   <si>
     <t xml:space="preserve">L1, L3</t>
@@ -277,7 +277,7 @@
     <t xml:space="preserve">L1210</t>
   </si>
   <si>
-    <t xml:space="preserve">C86069</t>
+    <t xml:space="preserve">C111247</t>
   </si>
   <si>
     <t xml:space="preserve">L2</t>
@@ -289,7 +289,7 @@
     <t xml:space="preserve">SMD-PIND-12.5x12.5x8_2.9x5.4</t>
   </si>
   <si>
-    <t xml:space="preserve">C169389</t>
+    <t xml:space="preserve">C2929503</t>
   </si>
   <si>
     <t xml:space="preserve">Q1</t>
@@ -343,7 +343,7 @@
     <t xml:space="preserve">C17414 </t>
   </si>
   <si>
-    <t xml:space="preserve">R2, R3, R3, R4, R6, R7, R8, R9, R35, R42, R44, R48, R49 </t>
+    <t xml:space="preserve">R2, R3, R4, R6, R7, R8, R9, R35, R42, R44, R48, R49 </t>
   </si>
   <si>
     <t xml:space="preserve">3.3KΩ</t>
@@ -373,13 +373,13 @@
     <t xml:space="preserve">T1</t>
   </si>
   <si>
-    <t xml:space="preserve">AP9T18GH-HF</t>
+    <t xml:space="preserve">NCE3050K</t>
   </si>
   <si>
     <t xml:space="preserve">TO-252-2</t>
   </si>
   <si>
-    <t xml:space="preserve">C124546</t>
+    <t xml:space="preserve">C108901 </t>
   </si>
 </sst>
 </file>
@@ -461,17 +461,25 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -483,6 +491,15 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -499,512 +516,515 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E33"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="2" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="2" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="79.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="4" t="s">
         <v>47</v>
       </c>
+      <c r="E13" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E19" s="0" t="s">
+      <c r="E19" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E21" s="0" t="s">
+      <c r="E21" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E23" s="0" t="s">
+      <c r="E23" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E24" s="0" t="s">
+      <c r="E24" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="3" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C27" s="0" t="s">
+      <c r="C27" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="0" t="s">
+      <c r="D27" s="1" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="0" t="s">
+      <c r="C28" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" s="1" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="C31" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="1" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="2" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="C32" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="1" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E33" s="0" t="s">
+      <c r="E33" s="1" t="s">
         <v>20</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
